--- a/data/dividends_info_20260330.xlsx
+++ b/data/dividends_info_20260330.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>28.29000091552734</v>
+        <v>27.91500091552734</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3181336058232586</v>
+        <v>0.3224072973249974</v>
       </c>
       <c r="J2" t="n">
         <v>350</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>50.5</v>
+        <v>50.90000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.386138613861386</v>
+        <v>1.375245538340704</v>
       </c>
       <c r="J3" t="n">
         <v>329</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.119999885559082</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6578947450975963</v>
+        <v>0.6593406317012648</v>
       </c>
       <c r="J4" t="n">
         <v>259</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28.31999969482422</v>
+        <v>27.91500091552734</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3177966135940617</v>
+        <v>0.3224072973249974</v>
       </c>
       <c r="J5" t="n">
         <v>259</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.96399998664856</v>
+        <v>1.973999977111816</v>
       </c>
       <c r="I6" t="n">
-        <v>3.920570291418157</v>
+        <v>3.900709265086196</v>
       </c>
       <c r="J6" t="n">
         <v>238</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5.409999847412109</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="I7" t="n">
-        <v>3.696857775248748</v>
+        <v>3.66300363741163</v>
       </c>
       <c r="J7" t="n">
         <v>231</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>28.31999969482422</v>
+        <v>27.91500091552734</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3177966135940617</v>
+        <v>0.3224072973249974</v>
       </c>
       <c r="J8" t="n">
         <v>175</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>9.279999732971191</v>
+        <v>9.404000282287598</v>
       </c>
       <c r="I9" t="n">
-        <v>2.801724218549686</v>
+        <v>2.764780861286331</v>
       </c>
       <c r="J9" t="n">
         <v>112</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.889999866485596</v>
+        <v>4.864999771118164</v>
       </c>
       <c r="I11" t="n">
-        <v>2.453987797063951</v>
+        <v>2.466598266096514</v>
       </c>
       <c r="J11" t="n">
         <v>105</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.119999885559082</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I12" t="n">
-        <v>4.009434178699683</v>
+        <v>4.047619231433834</v>
       </c>
       <c r="J12" t="n">
         <v>98</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>30.14999961853027</v>
+        <v>31.14999961853027</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4975124441056695</v>
+        <v>0.481540936876189</v>
       </c>
       <c r="J14" t="n">
         <v>98</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>21.97999954223633</v>
+        <v>22.1200008392334</v>
       </c>
       <c r="I15" t="n">
-        <v>1.137397657900789</v>
+        <v>1.130198872129266</v>
       </c>
       <c r="J15" t="n">
         <v>84</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>21.25</v>
+        <v>21.79999923706055</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9176470588235295</v>
+        <v>0.8944954441488928</v>
       </c>
       <c r="J16" t="n">
         <v>84</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5.164999961853027</v>
+        <v>5.150000095367432</v>
       </c>
       <c r="I17" t="n">
-        <v>5.614714465476158</v>
+        <v>5.631067856889227</v>
       </c>
       <c r="J17" t="n">
         <v>84</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3.936000108718872</v>
+        <v>3.98799991607666</v>
       </c>
       <c r="I18" t="n">
-        <v>4.065040538123318</v>
+        <v>4.012036192754131</v>
       </c>
       <c r="J18" t="n">
         <v>84</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.441999912261963</v>
+        <v>2.446000099182129</v>
       </c>
       <c r="I19" t="n">
-        <v>5.675675879595684</v>
+        <v>5.666393883072359</v>
       </c>
       <c r="J19" t="n">
         <v>84</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>55.52000045776367</v>
+        <v>55.65999984741211</v>
       </c>
       <c r="I20" t="n">
-        <v>1.134726215428018</v>
+        <v>1.131872083591627</v>
       </c>
       <c r="J20" t="n">
         <v>84</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>19.85499954223633</v>
+        <v>19.92000007629395</v>
       </c>
       <c r="I22" t="n">
-        <v>4.281037620735508</v>
+        <v>4.267068256749424</v>
       </c>
       <c r="J22" t="n">
         <v>84</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>28.31999969482422</v>
+        <v>27.91500091552734</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3177966135940617</v>
+        <v>0.3224072973249974</v>
       </c>
       <c r="J23" t="n">
         <v>84</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.46999979019165</v>
+        <v>6.526000022888184</v>
       </c>
       <c r="I24" t="n">
-        <v>2.802163923943955</v>
+        <v>2.778118286303083</v>
       </c>
       <c r="J24" t="n">
         <v>84</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7.579999923706055</v>
+        <v>7.800000190734863</v>
       </c>
       <c r="I25" t="n">
-        <v>3.430079190197134</v>
+        <v>3.33333325182271</v>
       </c>
       <c r="J25" t="n">
         <v>84</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>9.704000473022461</v>
+        <v>9.890000343322754</v>
       </c>
       <c r="I26" t="n">
-        <v>2.854492853437837</v>
+        <v>2.800808800649</v>
       </c>
       <c r="J26" t="n">
         <v>84</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>25.20000076293945</v>
+        <v>25.54999923706055</v>
       </c>
       <c r="I27" t="n">
-        <v>4.404761771406091</v>
+        <v>4.344422830314348</v>
       </c>
       <c r="J27" t="n">
         <v>66</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="I28" t="n">
-        <v>3.614457904003342</v>
+        <v>3.636363688907676</v>
       </c>
       <c r="J28" t="n">
         <v>63</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.4539999961853027</v>
+        <v>0.4709999859333038</v>
       </c>
       <c r="I29" t="n">
-        <v>5.066079337721495</v>
+        <v>4.883227322061305</v>
       </c>
       <c r="J29" t="n">
         <v>63</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.5</v>
+        <v>2.525000095367432</v>
       </c>
       <c r="I30" t="n">
-        <v>7.199999999999999</v>
+        <v>7.128712602040787</v>
       </c>
       <c r="J30" t="n">
         <v>56</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>12.10999965667725</v>
+        <v>12.18000030517578</v>
       </c>
       <c r="I31" t="n">
-        <v>2.064409637387184</v>
+        <v>2.052545104565923</v>
       </c>
       <c r="J31" t="n">
         <v>56</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3.400000095367432</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="I32" t="n">
-        <v>4.411764582135689</v>
+        <v>4.385964814437847</v>
       </c>
       <c r="J32" t="n">
         <v>56</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>13.35000038146973</v>
+        <v>13.30000019073486</v>
       </c>
       <c r="I33" t="n">
-        <v>4.344569164245573</v>
+        <v>4.360902193099543</v>
       </c>
       <c r="J33" t="n">
         <v>56</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.400000095367432</v>
+        <v>2.434999942779541</v>
       </c>
       <c r="I34" t="n">
-        <v>4.333333161142144</v>
+        <v>4.27104732829211</v>
       </c>
       <c r="J34" t="n">
         <v>49</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>9.067999839782715</v>
+        <v>9.21399974822998</v>
       </c>
       <c r="I35" t="n">
-        <v>3.198059165459236</v>
+        <v>3.147384501022038</v>
       </c>
       <c r="J35" t="n">
         <v>49</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.96399998664856</v>
+        <v>1.973999977111816</v>
       </c>
       <c r="I36" t="n">
-        <v>3.920570291418157</v>
+        <v>3.900709265086196</v>
       </c>
       <c r="J36" t="n">
         <v>49</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>33.65999984741211</v>
+        <v>34.18999862670898</v>
       </c>
       <c r="I37" t="n">
-        <v>4.872251953162408</v>
+        <v>4.796724381026571</v>
       </c>
       <c r="J37" t="n">
         <v>49</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>31.82500076293945</v>
+        <v>31.92000007629395</v>
       </c>
       <c r="I38" t="n">
-        <v>6.284367484851787</v>
+        <v>6.265664145425055</v>
       </c>
       <c r="J38" t="n">
         <v>49</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3.529999971389771</v>
+        <v>3.635999917984009</v>
       </c>
       <c r="I39" t="n">
-        <v>2.832861212761702</v>
+        <v>2.750275089539752</v>
       </c>
       <c r="J39" t="n">
         <v>49</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>31.14999961853027</v>
+        <v>32.15000152587891</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4765971165909269</v>
+        <v>0.461772917430496</v>
       </c>
       <c r="J40" t="n">
         <v>49</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>21.71999931335449</v>
+        <v>21.57999992370605</v>
       </c>
       <c r="I41" t="n">
-        <v>4.23572757405356</v>
+        <v>4.263206687917371</v>
       </c>
       <c r="J41" t="n">
         <v>49</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>7.980000019073486</v>
+        <v>8.034999847412109</v>
       </c>
       <c r="I42" t="n">
-        <v>3.759398487255033</v>
+        <v>3.733665285589559</v>
       </c>
       <c r="J42" t="n">
         <v>49</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>72.51999664306641</v>
+        <v>73.41999816894531</v>
       </c>
       <c r="I43" t="n">
-        <v>1.43408721475642</v>
+        <v>1.416507798879096</v>
       </c>
       <c r="J43" t="n">
         <v>49</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>50.5</v>
+        <v>50.90000152587891</v>
       </c>
       <c r="I44" t="n">
-        <v>4.356435643564357</v>
+        <v>4.3222002633565</v>
       </c>
       <c r="J44" t="n">
         <v>49</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>7.389999866485596</v>
+        <v>7.429999828338623</v>
       </c>
       <c r="I45" t="n">
-        <v>11.63734797750387</v>
+        <v>11.57469744104017</v>
       </c>
       <c r="J45" t="n">
         <v>49</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>10.77000045776367</v>
+        <v>10.94499969482422</v>
       </c>
       <c r="I46" t="n">
-        <v>5.199628376954413</v>
+        <v>5.116491691313783</v>
       </c>
       <c r="J46" t="n">
         <v>49</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.725000023841858</v>
+        <v>1.700000047683716</v>
       </c>
       <c r="I47" t="n">
-        <v>2.318840547660599</v>
+        <v>2.352941110472368</v>
       </c>
       <c r="J47" t="n">
         <v>49</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>8.439999580383301</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I48" t="n">
-        <v>3.554502546389648</v>
+        <v>3.488371938289734</v>
       </c>
       <c r="J48" t="n">
         <v>49</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2.190000057220459</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="I49" t="n">
-        <v>4.931506720464348</v>
+        <v>4.886877743701542</v>
       </c>
       <c r="J49" t="n">
         <v>49</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>64.19999694824219</v>
+        <v>65.69999694824219</v>
       </c>
       <c r="I50" t="n">
-        <v>3.208722893960205</v>
+        <v>3.13546437699662</v>
       </c>
       <c r="J50" t="n">
         <v>49</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>14.19999980926514</v>
+        <v>14.31999969482422</v>
       </c>
       <c r="I51" t="n">
-        <v>5.281690211788906</v>
+        <v>5.237430279213469</v>
       </c>
       <c r="J51" t="n">
         <v>49</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>15.10000038146973</v>
+        <v>15.18000030517578</v>
       </c>
       <c r="I52" t="n">
-        <v>1.986754916696235</v>
+        <v>1.976284545249395</v>
       </c>
       <c r="J52" t="n">
         <v>49</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>40.79999923706055</v>
+        <v>41.40000152587891</v>
       </c>
       <c r="I53" t="n">
-        <v>2.083333372290618</v>
+        <v>2.05314002094582</v>
       </c>
       <c r="J53" t="n">
         <v>49</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>28.68000030517578</v>
+        <v>28.79999923706055</v>
       </c>
       <c r="I54" t="n">
-        <v>2.963737764837483</v>
+        <v>2.951388967073996</v>
       </c>
       <c r="J54" t="n">
         <v>49</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>57.93999862670898</v>
+        <v>59</v>
       </c>
       <c r="I55" t="n">
-        <v>2.243700432883218</v>
+        <v>2.203389830508474</v>
       </c>
       <c r="J55" t="n">
         <v>49</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>6.840000152587891</v>
+        <v>6.860000133514404</v>
       </c>
       <c r="I56" t="n">
-        <v>8.771929628875695</v>
+        <v>8.746355514903142</v>
       </c>
       <c r="J56" t="n">
         <v>49</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>5.409999847412109</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="I57" t="n">
-        <v>3.696857775248748</v>
+        <v>3.66300363741163</v>
       </c>
       <c r="J57" t="n">
         <v>49</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>21.65999984741211</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="I58" t="n">
-        <v>4.616805203345733</v>
+        <v>4.566210125199586</v>
       </c>
       <c r="J58" t="n">
         <v>49</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>4.139999866485596</v>
+        <v>4.199999809265137</v>
       </c>
       <c r="I59" t="n">
-        <v>5.193236882456988</v>
+        <v>5.119047851519261</v>
       </c>
       <c r="J59" t="n">
         <v>49</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>9.399999618530273</v>
+        <v>9.25</v>
       </c>
       <c r="I60" t="n">
-        <v>2.553191592975032</v>
+        <v>2.594594594594594</v>
       </c>
       <c r="J60" t="n">
         <v>49</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>18.60000038146973</v>
+        <v>18.78000068664551</v>
       </c>
       <c r="I61" t="n">
-        <v>4.247311740848342</v>
+        <v>4.206602615098786</v>
       </c>
       <c r="J61" t="n">
         <v>49</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4.485000133514404</v>
+        <v>4.420000076293945</v>
       </c>
       <c r="I62" t="n">
-        <v>2.073578533589163</v>
+        <v>2.104072361871497</v>
       </c>
       <c r="J62" t="n">
         <v>49</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>32.47999954223633</v>
+        <v>32.61999893188477</v>
       </c>
       <c r="I63" t="n">
-        <v>1.077586222083738</v>
+        <v>1.072961408523802</v>
       </c>
       <c r="J63" t="n">
         <v>49</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1.940000057220459</v>
+        <v>1.950000047683716</v>
       </c>
       <c r="I64" t="n">
-        <v>3.092783413932739</v>
+        <v>3.076923001682502</v>
       </c>
       <c r="J64" t="n">
         <v>49</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>11.94999980926514</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I65" t="n">
-        <v>1.673640194077116</v>
+        <v>1.70940173726859</v>
       </c>
       <c r="J65" t="n">
         <v>49</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>5.494999885559082</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="I66" t="n">
-        <v>1.874431340220499</v>
+        <v>1.859205788975284</v>
       </c>
       <c r="J66" t="n">
         <v>49</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>5.109000205993652</v>
+        <v>5.104000091552734</v>
       </c>
       <c r="I67" t="n">
-        <v>3.718927233103268</v>
+        <v>3.722570466141947</v>
       </c>
       <c r="J67" t="n">
         <v>49</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>9.904999732971191</v>
+        <v>9.954999923706055</v>
       </c>
       <c r="I68" t="n">
-        <v>4.361433736964003</v>
+        <v>4.339527908697107</v>
       </c>
       <c r="J68" t="n">
         <v>49</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>24.79999923706055</v>
+        <v>24.6200008392334</v>
       </c>
       <c r="I69" t="n">
-        <v>1.774193602967835</v>
+        <v>1.787164845660096</v>
       </c>
       <c r="J69" t="n">
         <v>49</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>7.269999980926514</v>
+        <v>7.53000020980835</v>
       </c>
       <c r="I70" t="n">
-        <v>6.464924363591286</v>
+        <v>6.24169969328543</v>
       </c>
       <c r="J70" t="n">
         <v>49</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>50.34000015258789</v>
+        <v>50.86000061035156</v>
       </c>
       <c r="I71" t="n">
-        <v>2.781088589106864</v>
+        <v>2.752654312227942</v>
       </c>
       <c r="J71" t="n">
         <v>49</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>2.990999937057495</v>
+        <v>3.095999956130981</v>
       </c>
       <c r="I72" t="n">
-        <v>10.03009048188533</v>
+        <v>9.689922617922285</v>
       </c>
       <c r="J72" t="n">
         <v>49</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.75</v>
+        <v>10.80000019073486</v>
       </c>
       <c r="I73" t="n">
-        <v>1.021276595744681</v>
+        <v>1.111111091488183</v>
       </c>
       <c r="J73" t="n">
         <v>49</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>3.470000028610229</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="I74" t="n">
-        <v>4.899135406292396</v>
+        <v>4.98533711791938</v>
       </c>
       <c r="J74" t="n">
         <v>49</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>5.809999942779541</v>
+        <v>5.889999866485596</v>
       </c>
       <c r="I76" t="n">
-        <v>5.679862362307114</v>
+        <v>5.602716595593102</v>
       </c>
       <c r="J76" t="n">
         <v>49</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.9269999861717224</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="I77" t="n">
-        <v>7.551240673592938</v>
+        <v>7.526881662541449</v>
       </c>
       <c r="J77" t="n">
         <v>49</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>49.34000015258789</v>
+        <v>48.90000152587891</v>
       </c>
       <c r="I78" t="n">
-        <v>1.438994725991626</v>
+        <v>1.45194269497978</v>
       </c>
       <c r="J78" t="n">
         <v>49</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>77.44999694824219</v>
+        <v>78.59999847412109</v>
       </c>
       <c r="I79" t="n">
-        <v>1.743060107416363</v>
+        <v>1.71755728525171</v>
       </c>
       <c r="J79" t="n">
         <v>49</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>3.767999887466431</v>
+        <v>3.831000089645386</v>
       </c>
       <c r="I81" t="n">
-        <v>4.511677417121859</v>
+        <v>4.437483581884645</v>
       </c>
       <c r="J81" t="n">
         <v>49</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>55.29999923706055</v>
+        <v>58.5</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8137432300332155</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="J82" t="n">
         <v>49</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>5.099999904632568</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I83" t="n">
-        <v>0.784313740156468</v>
+        <v>0.8064516067008695</v>
       </c>
       <c r="J83" t="n">
         <v>49</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>29.75</v>
+        <v>30.79999923706055</v>
       </c>
       <c r="I84" t="n">
-        <v>3.529411764705882</v>
+        <v>3.409090993536689</v>
       </c>
       <c r="J84" t="n">
         <v>49</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>17.04000091552734</v>
+        <v>17.28000068664551</v>
       </c>
       <c r="I85" t="n">
-        <v>2.23004682854056</v>
+        <v>2.199073986690725</v>
       </c>
       <c r="J85" t="n">
         <v>49</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>25.38999938964844</v>
+        <v>25.36000061035156</v>
       </c>
       <c r="I86" t="n">
-        <v>2.363135149363656</v>
+        <v>2.365930542427074</v>
       </c>
       <c r="J86" t="n">
         <v>49</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>28.04999923706055</v>
+        <v>29.10000038146973</v>
       </c>
       <c r="I87" t="n">
-        <v>1.247771869945611</v>
+        <v>1.202749125126722</v>
       </c>
       <c r="J87" t="n">
         <v>49</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>19.21999931335449</v>
+        <v>19.67000007629395</v>
       </c>
       <c r="I88" t="n">
-        <v>5.827263475612086</v>
+        <v>5.693950155850843</v>
       </c>
       <c r="J88" t="n">
         <v>49</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>2.25600004196167</v>
+        <v>2.25</v>
       </c>
       <c r="I89" t="n">
-        <v>3.590425465132869</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="J89" t="n">
         <v>49</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>8.939999580383301</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I90" t="n">
-        <v>3.914988998075476</v>
+        <v>3.863134478914378</v>
       </c>
       <c r="J90" t="n">
         <v>42</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>6</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>5.050505001853162</v>
       </c>
       <c r="J92" t="n">
         <v>42</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>9.119999885559082</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6578947450975963</v>
+        <v>0.6593406317012648</v>
       </c>
       <c r="J93" t="n">
         <v>42</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>14.52000045776367</v>
+        <v>14.57999992370605</v>
       </c>
       <c r="I94" t="n">
-        <v>3.443526062236837</v>
+        <v>3.429355299152198</v>
       </c>
       <c r="J94" t="n">
         <v>42</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>4.599999904632568</v>
+        <v>4.420000076293945</v>
       </c>
       <c r="I96" t="n">
-        <v>2.06521743412054</v>
+        <v>2.149321229868734</v>
       </c>
       <c r="J96" t="n">
         <v>42</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>6.989999771118164</v>
+        <v>7.110000133514404</v>
       </c>
       <c r="I97" t="n">
-        <v>3.147353465003153</v>
+        <v>3.094233415875565</v>
       </c>
       <c r="J97" t="n">
         <v>42</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>3.394999980926514</v>
+        <v>3.365000009536743</v>
       </c>
       <c r="I98" t="n">
-        <v>4.712812986712747</v>
+        <v>4.754829109852724</v>
       </c>
       <c r="J98" t="n">
         <v>35</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>18.92000007629395</v>
+        <v>19.26000022888184</v>
       </c>
       <c r="I99" t="n">
-        <v>3.224101466914407</v>
+        <v>3.167185839828073</v>
       </c>
       <c r="J99" t="n">
         <v>35</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>11.75</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="I101" t="n">
-        <v>5.957446808510638</v>
+        <v>6.034482560174792</v>
       </c>
       <c r="J101" t="n">
         <v>35</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>8.380000114440918</v>
+        <v>8.449999809265137</v>
       </c>
       <c r="I102" t="n">
-        <v>6.091885358334014</v>
+        <v>6.041420254711179</v>
       </c>
       <c r="J102" t="n">
         <v>35</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7.434999942779541</v>
+        <v>7.355000019073486</v>
       </c>
       <c r="I103" t="n">
-        <v>3.631472791902426</v>
+        <v>3.6709721182844</v>
       </c>
       <c r="J103" t="n">
         <v>35</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>4.824999809265137</v>
+        <v>4.885000228881836</v>
       </c>
       <c r="I104" t="n">
-        <v>7.253886297112748</v>
+        <v>7.164789838302917</v>
       </c>
       <c r="J104" t="n">
         <v>35</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>38</v>
+        <v>37.79999923706055</v>
       </c>
       <c r="I105" t="n">
-        <v>2.894736842105263</v>
+        <v>2.910052968788207</v>
       </c>
       <c r="J105" t="n">
         <v>35</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>9.920000076293945</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="I107" t="n">
-        <v>4.334677386017173</v>
+        <v>4.257425581774359</v>
       </c>
       <c r="J107" t="n">
         <v>35</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>3.805000066757202</v>
+        <v>3.890000104904175</v>
       </c>
       <c r="I108" t="n">
-        <v>3.942181271177663</v>
+        <v>3.856041027117017</v>
       </c>
       <c r="J108" t="n">
         <v>35</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>12.22000026702881</v>
+        <v>12.47999954223633</v>
       </c>
       <c r="I109" t="n">
-        <v>1.613494236428032</v>
+        <v>1.579879865641956</v>
       </c>
       <c r="J109" t="n">
         <v>35</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>26.14999961853027</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="I110" t="n">
-        <v>4.206501017386341</v>
+        <v>4.166666726873379</v>
       </c>
       <c r="J110" t="n">
         <v>35</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>37</v>
+        <v>38.20000076293945</v>
       </c>
       <c r="I111" t="n">
-        <v>1.27027027027027</v>
+        <v>1.230366467573426</v>
       </c>
       <c r="J111" t="n">
         <v>35</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>2.460000038146973</v>
+        <v>2.5</v>
       </c>
       <c r="I112" t="n">
-        <v>4.471544646107361</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="J112" t="n">
         <v>35</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>74.90000152587891</v>
+        <v>76</v>
       </c>
       <c r="I113" t="n">
-        <v>1.602136148936372</v>
+        <v>1.578947368421053</v>
       </c>
       <c r="J113" t="n">
         <v>35</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>23.20000076293945</v>
+        <v>23.60000038146973</v>
       </c>
       <c r="I114" t="n">
-        <v>1.163793065176567</v>
+        <v>1.144067778117491</v>
       </c>
       <c r="J114" t="n">
         <v>35</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>10.44999980926514</v>
+        <v>10.39999961853027</v>
       </c>
       <c r="I115" t="n">
-        <v>3.636363702735056</v>
+        <v>3.653846287868437</v>
       </c>
       <c r="J115" t="n">
         <v>35</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>25.64999961853027</v>
+        <v>25.89999961853027</v>
       </c>
       <c r="I116" t="n">
-        <v>1.16959066066914</v>
+        <v>1.158301175361268</v>
       </c>
       <c r="J116" t="n">
         <v>35</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>0.148499995470047</v>
+        <v>0.1490000039339066</v>
       </c>
       <c r="I117" t="n">
-        <v>4.713804857598078</v>
+        <v>4.6979864531447</v>
       </c>
       <c r="J117" t="n">
         <v>28</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>6.320000171661377</v>
+        <v>6.190000057220459</v>
       </c>
       <c r="I118" t="n">
-        <v>2.531645500856685</v>
+        <v>2.584814192584127</v>
       </c>
       <c r="J118" t="n">
         <v>28</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>2.265000104904175</v>
+        <v>2.279999971389771</v>
       </c>
       <c r="I119" t="n">
-        <v>2.869757041479252</v>
+        <v>2.850877228756251</v>
       </c>
       <c r="J119" t="n">
         <v>28</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>1.330000042915344</v>
+        <v>1.320000052452087</v>
       </c>
       <c r="I121" t="n">
-        <v>5.263157724909606</v>
+        <v>5.30303009230682</v>
       </c>
       <c r="J121" t="n">
         <v>28</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>6.59499979019165</v>
+        <v>6.559999942779541</v>
       </c>
       <c r="I122" t="n">
-        <v>7.58150137841733</v>
+        <v>7.621951285995664</v>
       </c>
       <c r="J122" t="n">
         <v>21</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>16.86000061035156</v>
+        <v>17.22999954223633</v>
       </c>
       <c r="I123" t="n">
-        <v>3.855278626745235</v>
+        <v>3.772489943523439</v>
       </c>
       <c r="J123" t="n">
         <v>21</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>11.72500038146973</v>
+        <v>11.67500019073486</v>
       </c>
       <c r="I124" t="n">
-        <v>4.605543560181199</v>
+        <v>4.625267590389741</v>
       </c>
       <c r="J124" t="n">
         <v>21</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>6.119999885559082</v>
+        <v>6.162000179290771</v>
       </c>
       <c r="I125" t="n">
-        <v>1.633986958659309</v>
+        <v>1.622849676896791</v>
       </c>
       <c r="J125" t="n">
         <v>21</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>8.279999732971191</v>
+        <v>8.220000267028809</v>
       </c>
       <c r="I126" t="n">
-        <v>1.932367212077019</v>
+        <v>1.946471956233079</v>
       </c>
       <c r="J126" t="n">
         <v>21</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>277</v>
+        <v>289.8999938964844</v>
       </c>
       <c r="I127" t="n">
-        <v>1.305054151624549</v>
+        <v>1.246981744087522</v>
       </c>
       <c r="J127" t="n">
         <v>21</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>26</v>
+        <v>25.70000076293945</v>
       </c>
       <c r="I128" t="n">
-        <v>5.230769230769231</v>
+        <v>5.291828636679189</v>
       </c>
       <c r="J128" t="n">
         <v>21</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>13</v>
+        <v>13.02999973297119</v>
       </c>
       <c r="I129" t="n">
-        <v>4.5</v>
+        <v>4.489639385944978</v>
       </c>
       <c r="J129" t="n">
         <v>21</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>16.51000022888184</v>
+        <v>16.46999931335449</v>
       </c>
       <c r="I130" t="n">
-        <v>3.815869117299628</v>
+        <v>3.825136771494412</v>
       </c>
       <c r="J130" t="n">
         <v>21</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>94.86000061035156</v>
+        <v>94.95999908447266</v>
       </c>
       <c r="I131" t="n">
-        <v>0.9487665973109722</v>
+        <v>0.9477674901822563</v>
       </c>
       <c r="J131" t="n">
         <v>21</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>59.66999816894531</v>
+        <v>59.84000015258789</v>
       </c>
       <c r="I132" t="n">
-        <v>2.8838613252976</v>
+        <v>2.875668441865104</v>
       </c>
       <c r="J132" t="n">
         <v>21</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>23.20000076293945</v>
+        <v>23.39999961853027</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6034482560174793</v>
+        <v>0.5982906080440067</v>
       </c>
       <c r="J133" t="n">
         <v>14</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>1.470000028610229</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="I134" t="n">
-        <v>4.081632573621466</v>
+        <v>4.026845611810072</v>
       </c>
       <c r="J134" t="n">
         <v>14</v>
@@ -6773,12 +6773,8 @@
           <t>IT0005379604</t>
         </is>
       </c>
-      <c r="H135" t="n">
-        <v>1.934999942779541</v>
-      </c>
-      <c r="I135" t="n">
-        <v>1.757105995112358</v>
-      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="n">
         <v>0</v>
       </c>
@@ -6821,10 +6817,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>24.20499992370605</v>
+        <v>24.55500030517578</v>
       </c>
       <c r="I136" t="n">
-        <v>1.074158235156033</v>
+        <v>1.058847472077597</v>
       </c>
       <c r="J136" t="n">
         <v>-7</v>
@@ -6868,10 +6864,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>28.31999969482422</v>
+        <v>27.91500091552734</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3177966135940617</v>
+        <v>0.3224072973249974</v>
       </c>
       <c r="J137" t="n">
         <v>-7</v>
@@ -6891,7 +6887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C401"/>
+  <dimension ref="A1:C371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7016,7 +7012,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7033,7 +7029,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7050,7 +7046,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7067,7 +7063,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7084,7 +7080,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7101,7 +7097,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7111,14 +7107,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7128,14 +7124,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7152,7 +7148,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7162,14 +7158,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7179,14 +7175,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7203,7 +7199,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7220,7 +7216,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7237,7 +7233,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7247,14 +7243,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7264,7 +7260,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7318,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7356,7 +7352,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7373,7 +7369,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7390,7 +7386,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7407,7 +7403,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7526,7 +7522,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7536,14 +7532,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7560,7 +7556,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7570,14 +7566,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7594,7 +7590,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7611,7 +7607,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7628,7 +7624,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7645,7 +7641,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7655,14 +7651,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7672,14 +7668,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7696,7 +7692,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7849,7 +7845,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7883,7 +7879,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7893,14 +7889,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7910,14 +7906,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7934,7 +7930,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7951,7 +7947,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7968,7 +7964,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7985,7 +7981,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8002,7 +7998,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8019,7 +8015,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8036,7 +8032,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8046,14 +8042,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8063,14 +8059,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8080,7 +8076,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8097,14 +8093,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8121,7 +8117,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8138,7 +8134,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8148,7 +8144,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8168,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8189,7 +8185,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8199,14 +8195,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8223,7 +8219,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8240,7 +8236,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8257,7 +8253,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8274,7 +8270,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8284,14 +8280,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8301,7 +8297,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8355,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8376,7 +8372,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8461,7 +8457,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8471,14 +8467,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8522,7 +8518,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8542,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8556,14 +8552,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8573,7 +8569,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8695,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8716,7 +8712,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8750,7 +8746,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8760,14 +8756,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8777,14 +8773,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8794,14 +8790,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8811,14 +8807,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8828,14 +8824,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8845,14 +8841,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8869,7 +8865,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8879,14 +8875,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8896,14 +8892,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8913,14 +8909,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8937,7 +8933,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8954,7 +8950,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8964,36 +8960,36 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -9005,46 +9001,46 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9056,63 +9052,63 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9124,7 +9120,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9134,14 +9130,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9151,14 +9147,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9175,7 +9171,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9192,7 +9188,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9202,14 +9198,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9226,7 +9222,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9243,7 +9239,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9253,14 +9249,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9277,7 +9273,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9294,7 +9290,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9311,7 +9307,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9321,14 +9317,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9338,14 +9334,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9355,14 +9351,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9372,14 +9368,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9396,7 +9392,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9406,14 +9402,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9430,7 +9426,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9440,14 +9436,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9457,14 +9453,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9474,14 +9470,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9498,7 +9494,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9508,7 +9504,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9528,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9549,7 +9545,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9566,7 +9562,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9576,14 +9572,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9593,14 +9589,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9610,14 +9606,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9634,7 +9630,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -9651,7 +9647,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -9668,7 +9664,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -9678,14 +9674,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -9695,14 +9691,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -9712,14 +9708,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -9729,14 +9725,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -9753,7 +9749,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -9763,14 +9759,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -9780,14 +9776,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -9804,7 +9800,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -9821,7 +9817,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -9831,14 +9827,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -9855,7 +9851,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -9865,14 +9861,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -9882,14 +9878,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -9906,7 +9902,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -9923,7 +9919,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -9940,7 +9936,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -9957,7 +9953,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -9974,7 +9970,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -9991,7 +9987,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -10001,14 +9997,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -10018,14 +10014,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -10042,7 +10038,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -10059,7 +10055,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -10069,14 +10065,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -10093,7 +10089,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -10110,7 +10106,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -10127,7 +10123,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -10144,7 +10140,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -10161,7 +10157,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -10178,7 +10174,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -10195,7 +10191,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -10212,7 +10208,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -10229,7 +10225,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -10246,7 +10242,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -10263,7 +10259,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -10280,7 +10276,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -10297,7 +10293,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -10314,7 +10310,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -10331,7 +10327,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -10348,7 +10344,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -10365,7 +10361,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -10382,12 +10378,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -10399,29 +10395,29 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -10433,12 +10429,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -10450,12 +10446,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -10467,46 +10463,46 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -10518,12 +10514,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -10535,24 +10531,24 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -10562,14 +10558,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -10579,14 +10575,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -10596,14 +10592,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -10613,14 +10609,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -10630,14 +10626,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -10654,7 +10650,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -10664,14 +10660,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -10688,7 +10684,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -10705,7 +10701,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -10715,53 +10711,53 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10773,12 +10769,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -10790,12 +10786,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -10807,12 +10803,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -10824,12 +10820,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -10841,12 +10837,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -10858,29 +10854,29 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -10892,7 +10888,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -10909,7 +10905,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -10919,14 +10915,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -10943,7 +10939,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -10960,7 +10956,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -10970,14 +10966,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -10994,7 +10990,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -11028,7 +11024,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -11045,7 +11041,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -11062,7 +11058,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -11072,14 +11068,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -11089,19 +11085,19 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -11113,12 +11109,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -11130,12 +11126,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -11147,12 +11143,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -11164,46 +11160,46 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -11215,12 +11211,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -11232,12 +11228,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -11249,46 +11245,46 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -11300,12 +11296,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -11317,12 +11313,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -11334,12 +11330,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -11351,12 +11347,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -11368,12 +11364,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -11385,46 +11381,46 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -11436,7 +11432,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -11446,14 +11442,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -11470,7 +11466,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -11487,7 +11483,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -11504,7 +11500,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -11521,7 +11517,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -11538,7 +11534,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -11555,7 +11551,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -11572,7 +11568,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -11582,14 +11578,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -11606,7 +11602,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -11623,7 +11619,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -11640,7 +11636,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -11657,7 +11653,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -11674,7 +11670,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -11691,7 +11687,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -11701,14 +11697,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -11725,7 +11721,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -11742,7 +11738,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -11759,7 +11755,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -11769,14 +11765,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -11793,7 +11789,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -11803,14 +11799,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -11827,7 +11823,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -11844,7 +11840,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -11861,7 +11857,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -11878,7 +11874,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -11895,7 +11891,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -11912,7 +11908,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -11929,7 +11925,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -11946,7 +11942,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -11963,7 +11959,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -11980,7 +11976,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -11997,7 +11993,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -12014,7 +12010,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -12031,7 +12027,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -12048,7 +12044,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -12065,12 +12061,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -12082,12 +12078,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -12099,12 +12095,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -12116,12 +12112,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -12133,12 +12129,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -12150,12 +12146,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -12167,29 +12163,29 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -12201,12 +12197,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -12218,12 +12214,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -12235,7 +12231,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -12245,14 +12241,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -12262,14 +12258,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -12286,7 +12282,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -12303,7 +12299,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -12320,7 +12316,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -12337,7 +12333,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -12354,7 +12350,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -12364,14 +12360,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -12381,14 +12377,14 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -12398,14 +12394,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -12415,14 +12411,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -12439,7 +12435,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -12456,7 +12452,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -12473,7 +12469,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -12490,7 +12486,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -12500,14 +12496,14 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -12524,7 +12520,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -12541,7 +12537,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -12551,14 +12547,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -12575,7 +12571,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -12592,7 +12588,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -12609,7 +12605,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -12626,7 +12622,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -12636,14 +12632,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -12653,14 +12649,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -12677,7 +12673,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -12694,7 +12690,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -12704,14 +12700,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -12728,7 +12724,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -12745,7 +12741,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -12762,7 +12758,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -12779,7 +12775,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -12796,7 +12792,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -12813,7 +12809,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -12830,7 +12826,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -12847,7 +12843,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -12864,7 +12860,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -12881,7 +12877,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -12891,14 +12887,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -12915,7 +12911,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -12925,14 +12921,14 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -12942,14 +12938,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -12966,7 +12962,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -12983,7 +12979,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -13000,7 +12996,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -13017,7 +13013,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -13034,7 +13030,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -13044,14 +13040,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -13068,7 +13064,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -13085,7 +13081,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -13102,7 +13098,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -13119,7 +13115,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -13136,7 +13132,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -13153,7 +13149,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -13170,7 +13166,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -13187,7 +13183,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -13196,516 +13192,6 @@
         </is>
       </c>
       <c r="C371" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>G.M. Leather S.p.A.</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>GPI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Gentili Mosconi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Toscana Aeroporti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>T.P.S. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>DHH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>Datrix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>DiaSorin S.p.A</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>E-Globe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>BIESSE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>EL.EN. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>ELICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>ELICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>HERA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>ELSA Solutions S.p.A.</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>EUKEDOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>RECORDATI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>Racing Force S.p.A.</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>Renovalo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>SABAF S.p.A.</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>SOGES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>Snam S.p.A.</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>ENA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -13722,398 +13208,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Arterra Bioscience S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005386369</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005416281</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>42</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>RES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0005543613</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1.142857142857143</v>
-      </c>
-      <c r="I4" t="n">
-        <v>49</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NL0000226223</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>28.31999969482422</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>DOLLARI USA</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.3177966135940617</v>
-      </c>
-      <c r="I5" t="n">
-        <v>84</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NL0000226223</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-09-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>28.31999969482422</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>DOLLARI USA</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.3177966135940617</v>
-      </c>
-      <c r="I6" t="n">
-        <v>175</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NL0000226223</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-12-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>28.31999969482422</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>DOLLARI USA</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.3177966135940617</v>
-      </c>
-      <c r="I7" t="n">
-        <v>259</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NL0000226223</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2027-03-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2027-03-17</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>28.29000091552734</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>DOLLARI USA</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.3181336058232586</v>
-      </c>
-      <c r="I8" t="n">
-        <v>350</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Unipol S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IT0004810054</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>19.21999931335449</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>5.827263475612086</v>
-      </c>
-      <c r="I9" t="n">
-        <v>49</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14124,1625 +13221,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A2A S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ambromobiliare S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Arterra Bioscience S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BIESSE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BREMBO N.V.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>BUZZI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Bellini Nautica S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BolognaFiere S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CEMBRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CIRCLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Confinvest F.L. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>DHH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Datrix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DiaSorin S.p.A</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>E-Globe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>EL.EN. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ELICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ELICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ELSA Solutions S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ENA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>EUKEDOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>EUROTECH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>EdgeLab S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Energy S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Energy Time S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>F.I.L.A. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>FinecoBank S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>G.M. Leather S.p.A.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>GPI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Gentili Mosconi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>HERA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Haiki+ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>INNOVATEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Italian Wine Brands S.p.A.</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>KALEON S.P.A.</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Leone Film Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Lindbergh S.p.A.</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MIT SIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>MONDO TV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Maps S.p.A.</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Markbass S.p.A.</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Nexi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Novamarine S.p.A.</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>OPS Retail S.p.A.</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>PHILOGEN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>PLANETEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>PREMIA FINANCE S.P.A</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Pasquarelli Auto S.p.A.</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Porto Aviation Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>RECORDATI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Racing Force S.p.A.</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Renovalo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>SABAF S.p.A.</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>SOGES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Seri Industrial S.p.A.</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Seri Industrial S.p.A.</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Snam S.p.A.</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>T.P.S. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Toscana Aeroporti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Unipol S.p.A.</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Vimi Fasteners S.p.A.</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>WEBUILD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>WIIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>YOLO GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>doxee S.p.A.</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>